--- a/kaggle_results/T10-28-2025/results_v162_10s3.xlsx
+++ b/kaggle_results/T10-28-2025/results_v162_10s3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1.git_projs\MedicalQA\kaggle_results\T10-28-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA272FAE-764C-4D9F-8093-C85962950213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F744B737-A52A-4372-9153-75AC0677BBE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -402,7 +402,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -414,7 +414,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -723,7 +722,6 @@
   <cols>
     <col min="5" max="5" width="50.08203125" style="3" customWidth="1"/>
     <col min="6" max="6" width="64.58203125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -795,7 +793,7 @@
       <c r="G2" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" t="s">
         <v>18</v>
       </c>
       <c r="I2" t="s">
@@ -842,7 +840,7 @@
       <c r="G3" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" t="s">
         <v>24</v>
       </c>
       <c r="I3" t="s">
@@ -889,7 +887,7 @@
       <c r="G4" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" t="s">
         <v>32</v>
       </c>
       <c r="I4" t="s">
@@ -936,13 +934,13 @@
       <c r="G5" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" t="s">
         <v>39</v>
       </c>
       <c r="I5" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="5" t="s">
         <v>41</v>
       </c>
       <c r="K5">
@@ -983,13 +981,13 @@
       <c r="G6" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" t="s">
         <v>43</v>
       </c>
       <c r="I6" t="s">
         <v>46</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="5" t="s">
         <v>47</v>
       </c>
       <c r="K6">
@@ -1030,13 +1028,13 @@
       <c r="G7" t="s">
         <v>51</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" t="s">
         <v>49</v>
       </c>
       <c r="I7" t="s">
         <v>52</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="5" t="s">
         <v>53</v>
       </c>
       <c r="K7">
@@ -1077,13 +1075,13 @@
       <c r="G8" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" t="s">
         <v>58</v>
       </c>
       <c r="I8" t="s">
         <v>59</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="5" t="s">
         <v>60</v>
       </c>
       <c r="K8">
@@ -1124,13 +1122,13 @@
       <c r="G9" t="s">
         <v>64</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" t="s">
         <v>62</v>
       </c>
       <c r="I9" t="s">
         <v>65</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="5" t="s">
         <v>66</v>
       </c>
       <c r="K9">
@@ -1171,13 +1169,13 @@
       <c r="G10" t="s">
         <v>70</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" t="s">
         <v>71</v>
       </c>
       <c r="I10" t="s">
         <v>72</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="5" t="s">
         <v>72</v>
       </c>
       <c r="K10">
@@ -1218,7 +1216,7 @@
       <c r="G11" t="s">
         <v>76</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" t="s">
         <v>74</v>
       </c>
       <c r="I11" t="s">
